--- a/data/config/voucher_rules.xlsx
+++ b/data/config/voucher_rules.xlsx
@@ -135,8 +135,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="VoucherRules" displayName="VoucherRules" ref="A1:P5" headerRowCount="1">
-  <autoFilter ref="A1:P5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="VoucherRules" displayName="VoucherRules" ref="A1:P8" headerRowCount="1">
+  <autoFilter ref="A1:P8"/>
   <tableColumns count="16">
     <tableColumn id="1" name="rule_code"/>
     <tableColumn id="2" name="business_type"/>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -847,6 +847,214 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EXPENSE_STANDARD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>660201</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>管理费用-招待费</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>tax_excluded_amount</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>by_tax_rate</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>profit_center</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>cost_center</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>报销{vendor_name}费用，{description}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EXPENSE_STANDARD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>22210101</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>应交税费-应交增值税-进项税额</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>tax_amount</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>by_tax_rate</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>profit_center</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>报销{vendor_name}费用，{description}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EXPENSE_STANDARD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>220201</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>应付账款-员工报销</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>profit_center</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>报销{vendor_name}费用，{description}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
